--- a/data/trans_camb/IP16B98-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Provincia-trans_camb.xlsx
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 0,0</t>
+          <t>-64,81; 0,0</t>
         </is>
       </c>
     </row>
@@ -627,14 +627,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 0,0</t>
+          <t>-64,81; 0,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,45</t>
+          <t>0,0; 49,39</t>
         </is>
       </c>
     </row>
@@ -723,14 +723,14 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 97,81</t>
+          <t>0,0; 97,6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-65,69; 0,0</t>
+          <t>-48,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1107,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-65,69; 0,0</t>
+          <t>-48,18; 0,0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,17</t>
+          <t>0,0; 54,38</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,83</t>
+          <t>0,0; 75,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,93; 56,6</t>
+          <t>6,33; 57,18</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 204,65</t>
+          <t>0,0; 119,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 325,58</t>
+          <t>0,0; 312,75</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6,29; 129,55</t>
+          <t>6,75; 129,89</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 19,86</t>
+          <t>-3,8; 19,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 16,6</t>
+          <t>-10,27; 16,64</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 12,75</t>
+          <t>-4,84; 12,24</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 25,59</t>
+          <t>-4,0; 25,06</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 19,74</t>
+          <t>-10,9; 19,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 15,21</t>
+          <t>-4,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B98-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Provincia-trans_camb.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 0,0</t>
+          <t>-65,92; 0,0</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 0,0</t>
+          <t>-65,92; 0,0</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 0,0</t>
+          <t>-58,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 0,0</t>
+          <t>-58,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,38</t>
+          <t>0,0; 54,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6,33; 57,18</t>
+          <t>6,27; 56,0</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 119,19</t>
+          <t>0,0; 119,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6,75; 129,89</t>
+          <t>6,69; 126,49</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 19,37</t>
+          <t>-2,67; 19,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 16,64</t>
+          <t>-10,52; 15,53</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 12,24</t>
+          <t>-5,36; 12,75</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 25,06</t>
+          <t>-2,67; 24,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 19,98</t>
+          <t>-11,2; 18,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 14,21</t>
+          <t>-5,57; 15,08</t>
         </is>
       </c>
     </row>
